--- a/e_commerce_forms/002_gocardless_magazine_subscription_form--e_commerce_forms.xlsx
+++ b/e_commerce_forms/002_gocardless_magazine_subscription_form--e_commerce_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,7 +1110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1427,17 +1427,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>frequency_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>bank_transfer</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1466,29 +1466,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>paypal</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_type_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>credit_card</t>
+          <t>one_time_payment</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>One Time Payment</t>
         </is>
       </c>
     </row>
@@ -1500,29 +1500,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>one_time_payment</t>
+          <t>recurring_payment</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>One Time Payment</t>
+          <t>Recurring Payment</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>payment_type_choices</t>
+          <t>payment_status_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>recurring_payment</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Recurring Payment</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -1551,29 +1551,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Paid</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>payment_status_choices</t>
+          <t>subscription_status_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>failed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1585,29 +1585,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>subscription_status_choices</t>
+          <t>card_brand_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>visa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Visa</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>visa</t>
+          <t>mastercard</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Mastercard</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>mastercard</t>
+          <t>amex</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Amex</t>
         </is>
       </c>
     </row>
@@ -1653,29 +1653,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>amex</t>
+          <t>discover</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Amex</t>
+          <t>Discover</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>card_brand_choices</t>
+          <t>card_type_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>discover</t>
+          <t>credit</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Discover</t>
+          <t>Credit</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>credit</t>
+          <t>debit</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
     </row>
@@ -1704,27 +1704,10 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>debit</t>
+          <t>gift</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>card_type_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>gift</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
         <is>
           <t>Gift</t>
         </is>
